--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899941</v>
+        <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593419</v>
+        <v>593549</v>
       </c>
       <c r="R2" t="n">
-        <v>6982972</v>
+        <v>6982796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899922</v>
+        <v>128899941</v>
       </c>
       <c r="B3" t="n">
-        <v>75205</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593611</v>
+        <v>593419</v>
       </c>
       <c r="R3" t="n">
-        <v>6982599</v>
+        <v>6982972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899917</v>
+        <v>128899922</v>
       </c>
       <c r="B4" t="n">
-        <v>91522</v>
+        <v>75205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593549</v>
+        <v>593611</v>
       </c>
       <c r="R4" t="n">
-        <v>6982796</v>
+        <v>6982599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899944</v>
+        <v>128899924</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593418</v>
+        <v>593566</v>
       </c>
       <c r="R8" t="n">
-        <v>6983033</v>
+        <v>6982621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899924</v>
+        <v>128899944</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>91522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593566</v>
+        <v>593418</v>
       </c>
       <c r="R9" t="n">
-        <v>6982621</v>
+        <v>6983033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128899945</v>
+        <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>75205</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593391</v>
+        <v>593531</v>
       </c>
       <c r="R16" t="n">
-        <v>6983112</v>
+        <v>6982809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128899935</v>
+        <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>75205</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593531</v>
+        <v>593391</v>
       </c>
       <c r="R17" t="n">
-        <v>6982809</v>
+        <v>6983112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>75205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R3" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899922</v>
+        <v>128899941</v>
       </c>
       <c r="B4" t="n">
-        <v>75205</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593611</v>
+        <v>593419</v>
       </c>
       <c r="R4" t="n">
-        <v>6982599</v>
+        <v>6982972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899924</v>
+        <v>128899944</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593566</v>
+        <v>593418</v>
       </c>
       <c r="R8" t="n">
-        <v>6982621</v>
+        <v>6983033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899944</v>
+        <v>128899924</v>
       </c>
       <c r="B9" t="n">
-        <v>91522</v>
+        <v>80225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593418</v>
+        <v>593566</v>
       </c>
       <c r="R9" t="n">
-        <v>6983033</v>
+        <v>6982621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B18" t="n">
-        <v>91705</v>
+        <v>82979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R18" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B19" t="n">
-        <v>82979</v>
+        <v>91705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R19" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899922</v>
+        <v>128899941</v>
       </c>
       <c r="B3" t="n">
-        <v>75205</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593611</v>
+        <v>593419</v>
       </c>
       <c r="R3" t="n">
-        <v>6982599</v>
+        <v>6982972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>75209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R4" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899925</v>
+        <v>128899916</v>
       </c>
       <c r="B6" t="n">
-        <v>75205</v>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593550</v>
+        <v>593535</v>
       </c>
       <c r="R6" t="n">
-        <v>6982627</v>
+        <v>6982817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899916</v>
+        <v>128899925</v>
       </c>
       <c r="B7" t="n">
-        <v>91958</v>
+        <v>75209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593535</v>
+        <v>593550</v>
       </c>
       <c r="R7" t="n">
-        <v>6982817</v>
+        <v>6982627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128899944</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128899924</v>
       </c>
       <c r="B9" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899931</v>
+        <v>128899919</v>
       </c>
       <c r="B10" t="n">
-        <v>79376</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593513</v>
+        <v>593587</v>
       </c>
       <c r="R10" t="n">
-        <v>6982764</v>
+        <v>6982681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899919</v>
+        <v>128899931</v>
       </c>
       <c r="B11" t="n">
-        <v>91522</v>
+        <v>79380</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593587</v>
+        <v>593513</v>
       </c>
       <c r="R11" t="n">
-        <v>6982681</v>
+        <v>6982764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128899946</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128899949</v>
       </c>
       <c r="B13" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128899923</v>
       </c>
       <c r="B14" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128899950</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128899935</v>
+        <v>128899945</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>75209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593531</v>
+        <v>593391</v>
       </c>
       <c r="R16" t="n">
-        <v>6982809</v>
+        <v>6983112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128899945</v>
+        <v>128899935</v>
       </c>
       <c r="B17" t="n">
-        <v>75205</v>
+        <v>91508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593391</v>
+        <v>593531</v>
       </c>
       <c r="R17" t="n">
-        <v>6983112</v>
+        <v>6982809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B18" t="n">
-        <v>82979</v>
+        <v>91709</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R18" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B19" t="n">
-        <v>91705</v>
+        <v>82983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R19" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>128899947</v>
       </c>
       <c r="B20" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128899948</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128899921</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128899932</v>
       </c>
       <c r="B24" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>128899928</v>
       </c>
       <c r="B27" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899917</v>
+        <v>128899941</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593549</v>
+        <v>593419</v>
       </c>
       <c r="R2" t="n">
-        <v>6982796</v>
+        <v>6982972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>75209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R3" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B4" t="n">
-        <v>75209</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R4" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899916</v>
+        <v>128899925</v>
       </c>
       <c r="B6" t="n">
-        <v>91962</v>
+        <v>75209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593535</v>
+        <v>593550</v>
       </c>
       <c r="R6" t="n">
-        <v>6982817</v>
+        <v>6982627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899925</v>
+        <v>128899916</v>
       </c>
       <c r="B7" t="n">
-        <v>75209</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593550</v>
+        <v>593535</v>
       </c>
       <c r="R7" t="n">
-        <v>6982627</v>
+        <v>6982817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899944</v>
+        <v>128899924</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593418</v>
+        <v>593566</v>
       </c>
       <c r="R8" t="n">
-        <v>6983033</v>
+        <v>6982621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899924</v>
+        <v>128899944</v>
       </c>
       <c r="B9" t="n">
-        <v>80229</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593566</v>
+        <v>593418</v>
       </c>
       <c r="R9" t="n">
-        <v>6982621</v>
+        <v>6983033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899919</v>
+        <v>128899946</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593587</v>
+        <v>593378</v>
       </c>
       <c r="R10" t="n">
-        <v>6982681</v>
+        <v>6983141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899931</v>
+        <v>128899919</v>
       </c>
       <c r="B11" t="n">
-        <v>79380</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593513</v>
+        <v>593587</v>
       </c>
       <c r="R11" t="n">
-        <v>6982764</v>
+        <v>6982681</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899946</v>
+        <v>128899931</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79380</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593378</v>
+        <v>593513</v>
       </c>
       <c r="R12" t="n">
-        <v>6983141</v>
+        <v>6982764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>75209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R2" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B3" t="n">
-        <v>75209</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R3" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899917</v>
+        <v>128899941</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593549</v>
+        <v>593419</v>
       </c>
       <c r="R4" t="n">
-        <v>6982796</v>
+        <v>6982972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899946</v>
+        <v>128899931</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593378</v>
+        <v>593513</v>
       </c>
       <c r="R10" t="n">
-        <v>6983141</v>
+        <v>6982764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899931</v>
+        <v>128899946</v>
       </c>
       <c r="B12" t="n">
-        <v>79380</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593513</v>
+        <v>593378</v>
       </c>
       <c r="R12" t="n">
-        <v>6982764</v>
+        <v>6983141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128899945</v>
+        <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>75209</v>
+        <v>91508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593391</v>
+        <v>593531</v>
       </c>
       <c r="R16" t="n">
-        <v>6983112</v>
+        <v>6982809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128899935</v>
+        <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>91508</v>
+        <v>75209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593531</v>
+        <v>593391</v>
       </c>
       <c r="R17" t="n">
-        <v>6982809</v>
+        <v>6983112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B26" t="n">
-        <v>91804</v>
+        <v>91508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B27" t="n">
-        <v>91508</v>
+        <v>91804</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>75209</v>
+        <v>91531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R2" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899917</v>
+        <v>128899941</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593549</v>
+        <v>593419</v>
       </c>
       <c r="R3" t="n">
-        <v>6982796</v>
+        <v>6982972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>83005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R4" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128899925</v>
       </c>
       <c r="B6" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128899916</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128899924</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128899944</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899931</v>
+        <v>128899919</v>
       </c>
       <c r="B10" t="n">
-        <v>79380</v>
+        <v>91531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593513</v>
+        <v>593587</v>
       </c>
       <c r="R10" t="n">
-        <v>6982764</v>
+        <v>6982681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899919</v>
+        <v>128899946</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593587</v>
+        <v>593378</v>
       </c>
       <c r="R11" t="n">
-        <v>6982681</v>
+        <v>6983141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899946</v>
+        <v>128899931</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593378</v>
+        <v>593513</v>
       </c>
       <c r="R12" t="n">
-        <v>6983141</v>
+        <v>6982764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128899949</v>
+        <v>128899923</v>
       </c>
       <c r="B13" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593379</v>
+        <v>593595</v>
       </c>
       <c r="R13" t="n">
-        <v>6983183</v>
+        <v>6982605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899923</v>
+        <v>128899949</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593595</v>
+        <v>593379</v>
       </c>
       <c r="R14" t="n">
-        <v>6982605</v>
+        <v>6983183</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
         <v>128899950</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B18" t="n">
-        <v>91709</v>
+        <v>82892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R18" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B19" t="n">
-        <v>82983</v>
+        <v>91714</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R19" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>128899947</v>
       </c>
       <c r="B20" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128899948</v>
       </c>
       <c r="B22" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128899921</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128899932</v>
       </c>
       <c r="B24" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91508</v>
+        <v>91809</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B27" t="n">
-        <v>91804</v>
+        <v>91513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899917</v>
+        <v>128899941</v>
       </c>
       <c r="B2" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593549</v>
+        <v>593419</v>
       </c>
       <c r="R2" t="n">
-        <v>6982796</v>
+        <v>6982972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>83010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R3" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B4" t="n">
-        <v>83010</v>
+        <v>91538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R4" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899925</v>
+        <v>128899916</v>
       </c>
       <c r="B6" t="n">
-        <v>83010</v>
+        <v>91975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593550</v>
+        <v>593535</v>
       </c>
       <c r="R6" t="n">
-        <v>6982627</v>
+        <v>6982817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899916</v>
+        <v>128899925</v>
       </c>
       <c r="B7" t="n">
-        <v>91975</v>
+        <v>83010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593535</v>
+        <v>593550</v>
       </c>
       <c r="R7" t="n">
-        <v>6982817</v>
+        <v>6982627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128899945</v>
+        <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>83010</v>
+        <v>91520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593391</v>
+        <v>593531</v>
       </c>
       <c r="R16" t="n">
-        <v>6983112</v>
+        <v>6982809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128899935</v>
+        <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>91520</v>
+        <v>83010</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593531</v>
+        <v>593391</v>
       </c>
       <c r="R17" t="n">
-        <v>6982809</v>
+        <v>6983112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B26" t="n">
-        <v>91805</v>
+        <v>91520</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B27" t="n">
-        <v>91520</v>
+        <v>91805</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899941</v>
+        <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593419</v>
+        <v>593549</v>
       </c>
       <c r="R2" t="n">
-        <v>6982972</v>
+        <v>6982796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899922</v>
+        <v>128899941</v>
       </c>
       <c r="B3" t="n">
-        <v>83010</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593611</v>
+        <v>593419</v>
       </c>
       <c r="R3" t="n">
-        <v>6982599</v>
+        <v>6982972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899917</v>
+        <v>128899922</v>
       </c>
       <c r="B4" t="n">
-        <v>91538</v>
+        <v>83010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593549</v>
+        <v>593611</v>
       </c>
       <c r="R4" t="n">
-        <v>6982796</v>
+        <v>6982599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128899916</v>
       </c>
       <c r="B6" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128899944</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128899919</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128899940</v>
       </c>
       <c r="B19" t="n">
-        <v>91721</v>
+        <v>91724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B27" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899917</v>
+        <v>128899922</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>83011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593549</v>
+        <v>593611</v>
       </c>
       <c r="R2" t="n">
-        <v>6982796</v>
+        <v>6982599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
         <v>128899941</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B4" t="n">
-        <v>83010</v>
+        <v>91544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R4" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128899916</v>
       </c>
       <c r="B6" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128899925</v>
       </c>
       <c r="B7" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128899944</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128899924</v>
       </c>
       <c r="B9" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899919</v>
+        <v>128899931</v>
       </c>
       <c r="B10" t="n">
-        <v>91541</v>
+        <v>79291</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593587</v>
+        <v>593513</v>
       </c>
       <c r="R10" t="n">
-        <v>6982681</v>
+        <v>6982764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899931</v>
+        <v>128899919</v>
       </c>
       <c r="B11" t="n">
-        <v>79290</v>
+        <v>91544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593513</v>
+        <v>593587</v>
       </c>
       <c r="R11" t="n">
-        <v>6982764</v>
+        <v>6982681</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128899946</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128899949</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128899923</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128899950</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128899935</v>
+        <v>128899945</v>
       </c>
       <c r="B16" t="n">
-        <v>91523</v>
+        <v>83011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593531</v>
+        <v>593391</v>
       </c>
       <c r="R16" t="n">
-        <v>6982809</v>
+        <v>6983112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128899945</v>
+        <v>128899935</v>
       </c>
       <c r="B17" t="n">
-        <v>83010</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593391</v>
+        <v>593531</v>
       </c>
       <c r="R17" t="n">
-        <v>6983112</v>
+        <v>6982809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B18" t="n">
-        <v>82897</v>
+        <v>91727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R18" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B19" t="n">
-        <v>91724</v>
+        <v>82898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R19" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>128899947</v>
       </c>
       <c r="B20" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128899948</v>
       </c>
       <c r="B22" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128899921</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128899932</v>
       </c>
       <c r="B24" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B26" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B27" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>83011</v>
+        <v>91544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R2" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899917</v>
+        <v>128899922</v>
       </c>
       <c r="B4" t="n">
-        <v>91544</v>
+        <v>83011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593549</v>
+        <v>593611</v>
       </c>
       <c r="R4" t="n">
-        <v>6982796</v>
+        <v>6982599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899931</v>
+        <v>128899946</v>
       </c>
       <c r="B10" t="n">
-        <v>79291</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593513</v>
+        <v>593378</v>
       </c>
       <c r="R10" t="n">
-        <v>6982764</v>
+        <v>6983141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899919</v>
+        <v>128899931</v>
       </c>
       <c r="B11" t="n">
-        <v>91544</v>
+        <v>79291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593587</v>
+        <v>593513</v>
       </c>
       <c r="R11" t="n">
-        <v>6982681</v>
+        <v>6982764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899946</v>
+        <v>128899919</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593378</v>
+        <v>593587</v>
       </c>
       <c r="R12" t="n">
-        <v>6983141</v>
+        <v>6982681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128899945</v>
+        <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>83011</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593391</v>
+        <v>593531</v>
       </c>
       <c r="R16" t="n">
-        <v>6983112</v>
+        <v>6982809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128899935</v>
+        <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>83011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593531</v>
+        <v>593391</v>
       </c>
       <c r="R17" t="n">
-        <v>6982809</v>
+        <v>6983112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B27" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899946</v>
+        <v>128899919</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593378</v>
+        <v>593587</v>
       </c>
       <c r="R10" t="n">
-        <v>6983141</v>
+        <v>6982681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899931</v>
+        <v>128899946</v>
       </c>
       <c r="B11" t="n">
-        <v>79291</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593513</v>
+        <v>593378</v>
       </c>
       <c r="R11" t="n">
-        <v>6982764</v>
+        <v>6983141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899919</v>
+        <v>128899931</v>
       </c>
       <c r="B12" t="n">
-        <v>91544</v>
+        <v>79291</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593587</v>
+        <v>593513</v>
       </c>
       <c r="R12" t="n">
-        <v>6982681</v>
+        <v>6982764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B18" t="n">
-        <v>91727</v>
+        <v>82898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R18" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B19" t="n">
-        <v>82898</v>
+        <v>91727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R19" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>83011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R3" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899922</v>
+        <v>128899941</v>
       </c>
       <c r="B4" t="n">
-        <v>83011</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593611</v>
+        <v>593419</v>
       </c>
       <c r="R4" t="n">
-        <v>6982599</v>
+        <v>6982972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B18" t="n">
-        <v>82898</v>
+        <v>91727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R18" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B19" t="n">
-        <v>91727</v>
+        <v>82898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R19" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B26" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B27" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128899922</v>
       </c>
       <c r="B3" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128899941</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128899916</v>
       </c>
       <c r="B6" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128899925</v>
       </c>
       <c r="B7" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128899944</v>
       </c>
       <c r="B8" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128899924</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899919</v>
+        <v>128899931</v>
       </c>
       <c r="B10" t="n">
-        <v>91544</v>
+        <v>79295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593587</v>
+        <v>593513</v>
       </c>
       <c r="R10" t="n">
-        <v>6982681</v>
+        <v>6982764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>128899946</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899931</v>
+        <v>128899919</v>
       </c>
       <c r="B12" t="n">
-        <v>79291</v>
+        <v>91551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593513</v>
+        <v>593587</v>
       </c>
       <c r="R12" t="n">
-        <v>6982764</v>
+        <v>6982681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>128899949</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128899923</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128899950</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B18" t="n">
-        <v>91727</v>
+        <v>82902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R18" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B19" t="n">
-        <v>82898</v>
+        <v>91734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R19" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>128899947</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128899948</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128899921</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128899932</v>
       </c>
       <c r="B24" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>128899928</v>
       </c>
       <c r="B26" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>128899938</v>
       </c>
       <c r="B27" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899922</v>
+        <v>128899941</v>
       </c>
       <c r="B3" t="n">
-        <v>83015</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593611</v>
+        <v>593419</v>
       </c>
       <c r="R3" t="n">
-        <v>6982599</v>
+        <v>6982972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>83005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R4" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899916</v>
+        <v>128899925</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>83005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593535</v>
+        <v>593550</v>
       </c>
       <c r="R6" t="n">
-        <v>6982817</v>
+        <v>6982627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899925</v>
+        <v>128899916</v>
       </c>
       <c r="B7" t="n">
-        <v>83015</v>
+        <v>91995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593550</v>
+        <v>593535</v>
       </c>
       <c r="R7" t="n">
-        <v>6982627</v>
+        <v>6982817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899944</v>
+        <v>128899924</v>
       </c>
       <c r="B8" t="n">
-        <v>91551</v>
+        <v>80144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593418</v>
+        <v>593566</v>
       </c>
       <c r="R8" t="n">
-        <v>6983033</v>
+        <v>6982621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899924</v>
+        <v>128899944</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>91558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593566</v>
+        <v>593418</v>
       </c>
       <c r="R9" t="n">
-        <v>6982621</v>
+        <v>6983033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128899919</v>
       </c>
       <c r="B12" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B18" t="n">
-        <v>82902</v>
+        <v>91741</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R18" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B19" t="n">
-        <v>91734</v>
+        <v>82871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R19" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128899932</v>
       </c>
       <c r="B24" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B27" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899917</v>
+        <v>128899941</v>
       </c>
       <c r="B2" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593549</v>
+        <v>593419</v>
       </c>
       <c r="R2" t="n">
-        <v>6982796</v>
+        <v>6982972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>83007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R3" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B4" t="n">
-        <v>83005</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R4" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899925</v>
+        <v>128899916</v>
       </c>
       <c r="B6" t="n">
-        <v>83005</v>
+        <v>91997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593550</v>
+        <v>593535</v>
       </c>
       <c r="R6" t="n">
-        <v>6982627</v>
+        <v>6982817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899916</v>
+        <v>128899925</v>
       </c>
       <c r="B7" t="n">
-        <v>91995</v>
+        <v>83007</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593535</v>
+        <v>593550</v>
       </c>
       <c r="R7" t="n">
-        <v>6982817</v>
+        <v>6982627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128899924</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128899944</v>
       </c>
       <c r="B9" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899931</v>
+        <v>128899919</v>
       </c>
       <c r="B10" t="n">
-        <v>79295</v>
+        <v>91560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593513</v>
+        <v>593587</v>
       </c>
       <c r="R10" t="n">
-        <v>6982764</v>
+        <v>6982681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899946</v>
+        <v>128899931</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593378</v>
+        <v>593513</v>
       </c>
       <c r="R11" t="n">
-        <v>6983141</v>
+        <v>6982764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899919</v>
+        <v>128899946</v>
       </c>
       <c r="B12" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593587</v>
+        <v>593378</v>
       </c>
       <c r="R12" t="n">
-        <v>6982681</v>
+        <v>6983141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>128899949</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128899923</v>
       </c>
       <c r="B14" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128899950</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B18" t="n">
-        <v>91741</v>
+        <v>82873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R18" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B19" t="n">
-        <v>82871</v>
+        <v>91743</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R19" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2424,7 +2424,7 @@
         <v>128899947</v>
       </c>
       <c r="B20" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128899948</v>
       </c>
       <c r="B22" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128899921</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128899932</v>
       </c>
       <c r="B24" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B26" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899941</v>
+        <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593419</v>
+        <v>593549</v>
       </c>
       <c r="R2" t="n">
-        <v>6982972</v>
+        <v>6982796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899922</v>
+        <v>128899941</v>
       </c>
       <c r="B3" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593611</v>
+        <v>593419</v>
       </c>
       <c r="R3" t="n">
-        <v>6982599</v>
+        <v>6982972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899917</v>
+        <v>128899922</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>83007</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593549</v>
+        <v>593611</v>
       </c>
       <c r="R4" t="n">
-        <v>6982796</v>
+        <v>6982599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899919</v>
+        <v>128899946</v>
       </c>
       <c r="B10" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593587</v>
+        <v>593378</v>
       </c>
       <c r="R10" t="n">
-        <v>6982681</v>
+        <v>6983141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899931</v>
+        <v>128899919</v>
       </c>
       <c r="B11" t="n">
-        <v>79297</v>
+        <v>91560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593513</v>
+        <v>593587</v>
       </c>
       <c r="R11" t="n">
-        <v>6982764</v>
+        <v>6982681</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899946</v>
+        <v>128899931</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593378</v>
+        <v>593513</v>
       </c>
       <c r="R12" t="n">
-        <v>6983141</v>
+        <v>6982764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899928</v>
+        <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
         <v>593518</v>
       </c>
       <c r="R26" t="n">
-        <v>6982722</v>
+        <v>6982817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899938</v>
+        <v>128899928</v>
       </c>
       <c r="B27" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3138,7 +3138,7 @@
         <v>593518</v>
       </c>
       <c r="R27" t="n">
-        <v>6982817</v>
+        <v>6982722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899917</v>
+        <v>128899941</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593549</v>
+        <v>593419</v>
       </c>
       <c r="R2" t="n">
-        <v>6982796</v>
+        <v>6982972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R3" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B4" t="n">
-        <v>83007</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R4" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899916</v>
+        <v>128899925</v>
       </c>
       <c r="B6" t="n">
-        <v>91997</v>
+        <v>83007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593535</v>
+        <v>593550</v>
       </c>
       <c r="R6" t="n">
-        <v>6982817</v>
+        <v>6982627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899925</v>
+        <v>128899916</v>
       </c>
       <c r="B7" t="n">
-        <v>83007</v>
+        <v>91997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593550</v>
+        <v>593535</v>
       </c>
       <c r="R7" t="n">
-        <v>6982627</v>
+        <v>6982817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899941</v>
+        <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593419</v>
+        <v>593549</v>
       </c>
       <c r="R2" t="n">
-        <v>6982972</v>
+        <v>6982796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899922</v>
+        <v>128899941</v>
       </c>
       <c r="B3" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593611</v>
+        <v>593419</v>
       </c>
       <c r="R3" t="n">
-        <v>6982599</v>
+        <v>6982972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899917</v>
+        <v>128899922</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>83007</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593549</v>
+        <v>593611</v>
       </c>
       <c r="R4" t="n">
-        <v>6982796</v>
+        <v>6982599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128899916</v>
       </c>
       <c r="B7" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899924</v>
+        <v>128899944</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>91558</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593566</v>
+        <v>593418</v>
       </c>
       <c r="R8" t="n">
-        <v>6982621</v>
+        <v>6983033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899944</v>
+        <v>128899924</v>
       </c>
       <c r="B9" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593418</v>
+        <v>593566</v>
       </c>
       <c r="R9" t="n">
-        <v>6983033</v>
+        <v>6982621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899946</v>
+        <v>128899919</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593378</v>
+        <v>593587</v>
       </c>
       <c r="R10" t="n">
-        <v>6983141</v>
+        <v>6982681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899919</v>
+        <v>128899931</v>
       </c>
       <c r="B11" t="n">
-        <v>91560</v>
+        <v>79297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593587</v>
+        <v>593513</v>
       </c>
       <c r="R11" t="n">
-        <v>6982681</v>
+        <v>6982764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899931</v>
+        <v>128899946</v>
       </c>
       <c r="B12" t="n">
-        <v>79297</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593513</v>
+        <v>593378</v>
       </c>
       <c r="R12" t="n">
-        <v>6982764</v>
+        <v>6983141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128899935</v>
+        <v>128899945</v>
       </c>
       <c r="B16" t="n">
-        <v>91542</v>
+        <v>83007</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593531</v>
+        <v>593391</v>
       </c>
       <c r="R16" t="n">
-        <v>6982809</v>
+        <v>6983112</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128899945</v>
+        <v>128899935</v>
       </c>
       <c r="B17" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593391</v>
+        <v>593531</v>
       </c>
       <c r="R17" t="n">
-        <v>6983112</v>
+        <v>6982809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B18" t="n">
-        <v>82873</v>
+        <v>91752</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R18" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B19" t="n">
-        <v>91743</v>
+        <v>82873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R19" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>128899928</v>
       </c>
       <c r="B27" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899917</v>
+        <v>128899941</v>
       </c>
       <c r="B2" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593549</v>
+        <v>593419</v>
       </c>
       <c r="R2" t="n">
-        <v>6982796</v>
+        <v>6982972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R3" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B4" t="n">
-        <v>83007</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,23 +880,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -904,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R4" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1059,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899925</v>
+        <v>128899916</v>
       </c>
       <c r="B6" t="n">
-        <v>83007</v>
+        <v>91993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593550</v>
+        <v>593535</v>
       </c>
       <c r="R6" t="n">
-        <v>6982627</v>
+        <v>6982817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1156,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899916</v>
+        <v>128899925</v>
       </c>
       <c r="B7" t="n">
-        <v>91992</v>
+        <v>83007</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593535</v>
+        <v>593550</v>
       </c>
       <c r="R7" t="n">
-        <v>6982817</v>
+        <v>6982627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1253,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899944</v>
+        <v>128899924</v>
       </c>
       <c r="B8" t="n">
-        <v>91558</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1264,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593418</v>
+        <v>593566</v>
       </c>
       <c r="R8" t="n">
-        <v>6983033</v>
+        <v>6982621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1350,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899924</v>
+        <v>128899944</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,23 +1361,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1389,10 +1381,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593566</v>
+        <v>593418</v>
       </c>
       <c r="R9" t="n">
-        <v>6982621</v>
+        <v>6983033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1443,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899919</v>
+        <v>128899931</v>
       </c>
       <c r="B10" t="n">
-        <v>91558</v>
+        <v>79297</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1478,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593587</v>
+        <v>593513</v>
       </c>
       <c r="R10" t="n">
-        <v>6982681</v>
+        <v>6982764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1540,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899931</v>
+        <v>128899946</v>
       </c>
       <c r="B11" t="n">
-        <v>79297</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1575,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593513</v>
+        <v>593378</v>
       </c>
       <c r="R11" t="n">
-        <v>6982764</v>
+        <v>6983141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1637,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899946</v>
+        <v>128899919</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,23 +1648,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1680,10 +1668,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593378</v>
+        <v>593587</v>
       </c>
       <c r="R12" t="n">
-        <v>6983141</v>
+        <v>6982681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2230,7 +2218,7 @@
         <v>128899940</v>
       </c>
       <c r="B18" t="n">
-        <v>91752</v>
+        <v>91753</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2909,7 +2897,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +2994,7 @@
         <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899924</v>
+        <v>128899944</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,23 +1264,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1284,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593566</v>
+        <v>593418</v>
       </c>
       <c r="R8" t="n">
-        <v>6982621</v>
+        <v>6983033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,10 +1346,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899944</v>
+        <v>128899924</v>
       </c>
       <c r="B9" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1361,19 +1357,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593418</v>
+        <v>593566</v>
       </c>
       <c r="R9" t="n">
-        <v>6983033</v>
+        <v>6982621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128899945</v>
+        <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593391</v>
+        <v>593531</v>
       </c>
       <c r="R16" t="n">
-        <v>6983112</v>
+        <v>6982809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128899935</v>
+        <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>83007</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593531</v>
+        <v>593391</v>
       </c>
       <c r="R17" t="n">
-        <v>6982809</v>
+        <v>6983112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2215,32 +2215,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B18" t="n">
-        <v>91753</v>
+        <v>82873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R18" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2312,32 +2312,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B19" t="n">
-        <v>82873</v>
+        <v>91753</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R19" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2897,7 +2897,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899941</v>
+        <v>128899917</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593419</v>
+        <v>593549</v>
       </c>
       <c r="R2" t="n">
-        <v>6982972</v>
+        <v>6982796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899922</v>
+        <v>128899941</v>
       </c>
       <c r="B3" t="n">
-        <v>83007</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +779,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593611</v>
+        <v>593419</v>
       </c>
       <c r="R3" t="n">
-        <v>6982599</v>
+        <v>6982972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899917</v>
+        <v>128899922</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>83011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,19 +876,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593549</v>
+        <v>593611</v>
       </c>
       <c r="R4" t="n">
-        <v>6982796</v>
+        <v>6982599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +965,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>128899916</v>
       </c>
       <c r="B6" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>128899925</v>
       </c>
       <c r="B7" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899944</v>
+        <v>128899924</v>
       </c>
       <c r="B8" t="n">
-        <v>91560</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,19 +1264,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1284,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593418</v>
+        <v>593566</v>
       </c>
       <c r="R8" t="n">
-        <v>6983033</v>
+        <v>6982621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,10 +1350,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899924</v>
+        <v>128899944</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>91563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,23 +1361,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593566</v>
+        <v>593418</v>
       </c>
       <c r="R9" t="n">
-        <v>6982621</v>
+        <v>6983033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,34 +1443,30 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899931</v>
+        <v>128899919</v>
       </c>
       <c r="B10" t="n">
-        <v>79297</v>
+        <v>91563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1478,10 +1474,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593513</v>
+        <v>593587</v>
       </c>
       <c r="R10" t="n">
-        <v>6982764</v>
+        <v>6982681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1540,32 +1536,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899946</v>
+        <v>128899931</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1575,10 +1571,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593378</v>
+        <v>593513</v>
       </c>
       <c r="R11" t="n">
-        <v>6983141</v>
+        <v>6982764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1637,10 +1633,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899919</v>
+        <v>128899946</v>
       </c>
       <c r="B12" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1648,19 +1644,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593587</v>
+        <v>593378</v>
       </c>
       <c r="R12" t="n">
-        <v>6982681</v>
+        <v>6983141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
         <v>128899949</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>128899923</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128899950</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2215,32 +2215,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899939</v>
+        <v>128899940</v>
       </c>
       <c r="B18" t="n">
-        <v>82873</v>
+        <v>91756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593477</v>
+        <v>593459</v>
       </c>
       <c r="R18" t="n">
-        <v>6982901</v>
+        <v>6982918</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2312,32 +2312,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899940</v>
+        <v>128899939</v>
       </c>
       <c r="B19" t="n">
-        <v>91753</v>
+        <v>82877</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593459</v>
+        <v>593477</v>
       </c>
       <c r="R19" t="n">
-        <v>6982918</v>
+        <v>6982901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2412,7 +2412,7 @@
         <v>128899947</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>128899948</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>128899921</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>128899932</v>
       </c>
       <c r="B24" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>128899928</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899917</v>
+        <v>128899941</v>
       </c>
       <c r="B2" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593549</v>
+        <v>593419</v>
       </c>
       <c r="R2" t="n">
-        <v>6982796</v>
+        <v>6982972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899941</v>
+        <v>128899922</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>83012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593419</v>
+        <v>593611</v>
       </c>
       <c r="R3" t="n">
-        <v>6982972</v>
+        <v>6982599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899922</v>
+        <v>128899917</v>
       </c>
       <c r="B4" t="n">
-        <v>83011</v>
+        <v>91565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,23 +880,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593611</v>
+        <v>593549</v>
       </c>
       <c r="R4" t="n">
-        <v>6982599</v>
+        <v>6982796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +965,7 @@
         <v>128899927</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>128899916</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>128899925</v>
       </c>
       <c r="B7" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899924</v>
+        <v>128899944</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>91565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,23 +1264,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1284,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593566</v>
+        <v>593418</v>
       </c>
       <c r="R8" t="n">
-        <v>6982621</v>
+        <v>6983033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,10 +1346,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899944</v>
+        <v>128899924</v>
       </c>
       <c r="B9" t="n">
-        <v>91563</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1361,19 +1357,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593418</v>
+        <v>593566</v>
       </c>
       <c r="R9" t="n">
-        <v>6983033</v>
+        <v>6982621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899919</v>
+        <v>128899946</v>
       </c>
       <c r="B10" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1454,19 +1454,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1474,10 +1478,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593587</v>
+        <v>593378</v>
       </c>
       <c r="R10" t="n">
-        <v>6982681</v>
+        <v>6983141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,34 +1540,30 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899931</v>
+        <v>128899919</v>
       </c>
       <c r="B11" t="n">
-        <v>79299</v>
+        <v>91565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593513</v>
+        <v>593587</v>
       </c>
       <c r="R11" t="n">
-        <v>6982764</v>
+        <v>6982681</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,32 +1633,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899946</v>
+        <v>128899931</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79300</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593378</v>
+        <v>593513</v>
       </c>
       <c r="R12" t="n">
-        <v>6983141</v>
+        <v>6982764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
         <v>128899949</v>
       </c>
       <c r="B13" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>128899923</v>
       </c>
       <c r="B14" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128899950</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128899935</v>
       </c>
       <c r="B16" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128899945</v>
       </c>
       <c r="B17" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128899940</v>
       </c>
       <c r="B18" t="n">
-        <v>91756</v>
+        <v>91758</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>128899939</v>
       </c>
       <c r="B19" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>128899947</v>
       </c>
       <c r="B20" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>128899936</v>
       </c>
       <c r="B21" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>128899948</v>
       </c>
       <c r="B22" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>128899921</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>128899932</v>
       </c>
       <c r="B24" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>128899918</v>
       </c>
       <c r="B25" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128899938</v>
       </c>
       <c r="B26" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>128899928</v>
       </c>
       <c r="B27" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128899941</v>
+        <v>128899940</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593419</v>
+        <v>593459</v>
       </c>
       <c r="R2" t="n">
-        <v>6982972</v>
+        <v>6982918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128899922</v>
+        <v>128899938</v>
       </c>
       <c r="B3" t="n">
-        <v>83012</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593611</v>
+        <v>593518</v>
       </c>
       <c r="R3" t="n">
-        <v>6982599</v>
+        <v>6982817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128899917</v>
+        <v>128899927</v>
       </c>
       <c r="B4" t="n">
-        <v>91565</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,19 +880,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593549</v>
+        <v>593529</v>
       </c>
       <c r="R4" t="n">
-        <v>6982796</v>
+        <v>6982652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128899927</v>
+        <v>128899928</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593529</v>
+        <v>593518</v>
       </c>
       <c r="R5" t="n">
-        <v>6982652</v>
+        <v>6982722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128899916</v>
+        <v>128899935</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593535</v>
+        <v>593531</v>
       </c>
       <c r="R6" t="n">
-        <v>6982817</v>
+        <v>6982809</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128899925</v>
+        <v>128899936</v>
       </c>
       <c r="B7" t="n">
-        <v>83012</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1167,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1191,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593550</v>
+        <v>593518</v>
       </c>
       <c r="R7" t="n">
-        <v>6982627</v>
+        <v>6982817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128899944</v>
+        <v>128899916</v>
       </c>
       <c r="B8" t="n">
-        <v>91565</v>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,19 +1268,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1284,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593418</v>
+        <v>593535</v>
       </c>
       <c r="R8" t="n">
-        <v>6983033</v>
+        <v>6982817</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128899924</v>
+        <v>128899932</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1381,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593566</v>
+        <v>593513</v>
       </c>
       <c r="R9" t="n">
-        <v>6982621</v>
+        <v>6982764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128899946</v>
+        <v>128899939</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1454,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1478,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593378</v>
+        <v>593477</v>
       </c>
       <c r="R10" t="n">
-        <v>6983141</v>
+        <v>6982901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1540,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128899919</v>
+        <v>128899929</v>
       </c>
       <c r="B11" t="n">
-        <v>91565</v>
+        <v>83312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1551,19 +1559,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1571,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593587</v>
+        <v>593525</v>
       </c>
       <c r="R11" t="n">
-        <v>6982681</v>
+        <v>6982732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128899931</v>
+        <v>128899933</v>
       </c>
       <c r="B12" t="n">
-        <v>79300</v>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6459</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1671,7 +1683,7 @@
         <v>593513</v>
       </c>
       <c r="R12" t="n">
-        <v>6982764</v>
+        <v>6982778</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128899949</v>
+        <v>128899930</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>92097</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1741,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1765,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593379</v>
+        <v>593528</v>
       </c>
       <c r="R13" t="n">
-        <v>6983183</v>
+        <v>6982740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1827,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128899923</v>
+        <v>128899921</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1862,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593595</v>
+        <v>593623</v>
       </c>
       <c r="R14" t="n">
-        <v>6982605</v>
+        <v>6982633</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1924,14 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128899950</v>
+        <v>128899926</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1959,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593379</v>
+        <v>593503</v>
       </c>
       <c r="R15" t="n">
-        <v>6983200</v>
+        <v>6982666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2021,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128899935</v>
+        <v>128899941</v>
       </c>
       <c r="B16" t="n">
-        <v>91545</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2056,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593531</v>
+        <v>593419</v>
       </c>
       <c r="R16" t="n">
-        <v>6982809</v>
+        <v>6982972</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2118,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128899945</v>
+        <v>128899946</v>
       </c>
       <c r="B17" t="n">
-        <v>83012</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2153,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593391</v>
+        <v>593378</v>
       </c>
       <c r="R17" t="n">
-        <v>6983112</v>
+        <v>6983141</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2215,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128899940</v>
+        <v>128899950</v>
       </c>
       <c r="B18" t="n">
-        <v>91758</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2226,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2250,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593459</v>
+        <v>593379</v>
       </c>
       <c r="R18" t="n">
-        <v>6982918</v>
+        <v>6983200</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2312,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128899939</v>
+        <v>128899922</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2323,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2347,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593477</v>
+        <v>593611</v>
       </c>
       <c r="R19" t="n">
-        <v>6982901</v>
+        <v>6982599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2409,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128899947</v>
+        <v>128899925</v>
       </c>
       <c r="B20" t="n">
-        <v>80184</v>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2444,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593393</v>
+        <v>593550</v>
       </c>
       <c r="R20" t="n">
-        <v>6983168</v>
+        <v>6982627</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2506,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128899936</v>
+        <v>128899934</v>
       </c>
       <c r="B21" t="n">
-        <v>91545</v>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2517,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2541,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593518</v>
+        <v>593513</v>
       </c>
       <c r="R21" t="n">
-        <v>6982817</v>
+        <v>6982778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2603,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128899948</v>
+        <v>128899945</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2614,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2638,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593393</v>
+        <v>593391</v>
       </c>
       <c r="R22" t="n">
-        <v>6983168</v>
+        <v>6983112</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2700,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128899921</v>
+        <v>128899923</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2711,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2735,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593623</v>
+        <v>593595</v>
       </c>
       <c r="R23" t="n">
-        <v>6982633</v>
+        <v>6982605</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2797,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128899932</v>
+        <v>128899924</v>
       </c>
       <c r="B24" t="n">
-        <v>82878</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2808,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2832,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593513</v>
+        <v>593566</v>
       </c>
       <c r="R24" t="n">
-        <v>6982764</v>
+        <v>6982621</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2894,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128899918</v>
+        <v>128899948</v>
       </c>
       <c r="B25" t="n">
-        <v>98712</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2929,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593561</v>
+        <v>593393</v>
       </c>
       <c r="R25" t="n">
-        <v>6982769</v>
+        <v>6983168</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2991,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128899938</v>
+        <v>128899949</v>
       </c>
       <c r="B26" t="n">
-        <v>91843</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3002,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3026,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>593518</v>
+        <v>593379</v>
       </c>
       <c r="R26" t="n">
-        <v>6982817</v>
+        <v>6983183</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3088,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128899928</v>
+        <v>128899931</v>
       </c>
       <c r="B27" t="n">
-        <v>91545</v>
+        <v>79583</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3123,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>593518</v>
+        <v>593513</v>
       </c>
       <c r="R27" t="n">
-        <v>6982722</v>
+        <v>6982764</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3182,6 +3194,200 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128899947</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lillsjöbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>593393</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6983168</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128899918</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lillsjöbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>593561</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6982769</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19727-2025 artfynd.xlsx
+++ b/artfynd/A 19727-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899940</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899938</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899927</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899928</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899935</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899936</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899916</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899932</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899939</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899929</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899933</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899930</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899921</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899926</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899941</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899946</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899950</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899922</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899925</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899934</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899945</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899923</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899924</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899948</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899949</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899931</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899947</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,8 +3528,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128899918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>